--- a/utils/monday_sprint_sprint_2023-17.xlsx
+++ b/utils/monday_sprint_sprint_2023-17.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="166">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>21522</t>
+    <t>4901490933</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>31/07/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>24/08/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,13 +102,16 @@
     <t>Julho</t>
   </si>
   <si>
-    <t>21524</t>
+    <t>4901498647</t>
   </si>
   <si>
     <t>Criar KB para receber os processos do novo custeio e aplicar padrão na nova KB</t>
   </si>
   <si>
-    <t>21523</t>
+    <t>23/08/2023</t>
+  </si>
+  <si>
+    <t>4908590752</t>
   </si>
   <si>
     <t>Criar KB para receber os processos do novo custeio</t>
@@ -123,7 +126,7 @@
     <t>Agosto</t>
   </si>
   <si>
-    <t>21422</t>
+    <t>4890567583</t>
   </si>
   <si>
     <t>Sistema de desmoldagem</t>
@@ -132,10 +135,13 @@
     <t>28/07/2023</t>
   </si>
   <si>
+    <t>26/08/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>21779</t>
+    <t>4974792223</t>
   </si>
   <si>
     <t>Correção</t>
@@ -147,58 +153,70 @@
     <t>11/08/2023</t>
   </si>
   <si>
+    <t>14/08/2023</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
-    <t>21768</t>
+    <t>4974803798</t>
   </si>
   <si>
     <t>Apontamento Eletrônico</t>
   </si>
   <si>
-    <t>21738</t>
+    <t>27/08/2023</t>
+  </si>
+  <si>
+    <t>4974982757</t>
   </si>
   <si>
     <t>Cópia de dados do desenho 3D no setor 501</t>
   </si>
   <si>
-    <t>21721</t>
+    <t>4974992562</t>
   </si>
   <si>
     <t>Movimentação Pré-Produtivo</t>
   </si>
   <si>
-    <t>21717</t>
+    <t>17/08/2023</t>
+  </si>
+  <si>
+    <t>4975012587</t>
   </si>
   <si>
     <t>ALTERAÇÃO RELATÓRIO ETIQUETA AMARELA - INCLUSÃO AMOSTRA</t>
   </si>
   <si>
-    <t>21695</t>
+    <t>4975060819</t>
   </si>
   <si>
     <t>Baixa depósito MPS KOM / 58F4600480</t>
   </si>
   <si>
-    <t>21795</t>
+    <t>4975404292</t>
   </si>
   <si>
     <t>Revisão Etiqueta Dimensional</t>
   </si>
   <si>
-    <t>21747</t>
+    <t>4974970464</t>
   </si>
   <si>
     <t>Data nos relatórios de Vendas</t>
   </si>
   <si>
-    <t>21697</t>
+    <t>15/08/2023</t>
+  </si>
+  <si>
+    <t>4975023280</t>
   </si>
   <si>
     <t>Ajuste de Impressão de Etiqueta padrão Altona</t>
   </si>
   <si>
-    <t>18923</t>
+    <t>4975297363</t>
   </si>
   <si>
     <t>Erro ao preencher MPO eletrônica</t>
@@ -207,37 +225,40 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>21808</t>
+    <t>16/08/2023</t>
+  </si>
+  <si>
+    <t>4975470431</t>
   </si>
   <si>
     <t>Padronizar Tela e Plano de Fundo sistema MPO</t>
   </si>
   <si>
-    <t>21693</t>
+    <t>4975076905</t>
   </si>
   <si>
     <t>Chamado Sistemas de materiais</t>
   </si>
   <si>
-    <t>21626</t>
+    <t>4975149668</t>
   </si>
   <si>
     <t>CÓPIA DE ANEXOS DA OTF</t>
   </si>
   <si>
-    <t>21611</t>
+    <t>4975178135</t>
   </si>
   <si>
     <t>Relação de Fornecedores</t>
   </si>
   <si>
-    <t>21278</t>
+    <t>4975381477</t>
   </si>
   <si>
     <t>Tabela de Faturamento</t>
   </si>
   <si>
-    <t>21782</t>
+    <t>4974763595</t>
   </si>
   <si>
     <t>Diferença - Estoque Processo</t>
@@ -249,25 +270,25 @@
     <t>Atualização campos da tabela do MPS</t>
   </si>
   <si>
-    <t>14/08/2023</t>
-  </si>
-  <si>
-    <t>21088</t>
+    <t>4986566708</t>
   </si>
   <si>
     <t>Sistema de controle de peças a serem destruídas (Final)</t>
   </si>
   <si>
-    <t>18941</t>
+    <t>4986779367</t>
   </si>
   <si>
     <t>Alteração de todas as rotinas que calculam a data prevista de liberação</t>
   </si>
   <si>
+    <t>4986796325</t>
+  </si>
+  <si>
     <t>Alteração de todas as telas de visualização dos fluxos</t>
   </si>
   <si>
-    <t>19378</t>
+    <t>4924698631</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -279,69 +300,105 @@
     <t>03/08/2023</t>
   </si>
   <si>
-    <t>21798</t>
+    <t>4974698801</t>
   </si>
   <si>
     <t>Tablet de Ajustagem</t>
   </si>
   <si>
-    <t>21101</t>
+    <t>4975145806</t>
   </si>
   <si>
     <t>Relatório das informações "F9" do SPS - Criar Base</t>
   </si>
   <si>
+    <t>4975368754</t>
+  </si>
+  <si>
     <t>Impressão de etiquetas via BlueTooth</t>
   </si>
   <si>
-    <t>21765</t>
+    <t>4974957755</t>
   </si>
   <si>
     <t>APROVAÇÃO DE SIC - Por ResponsavelDE Centro De Custo</t>
   </si>
   <si>
-    <t>18629</t>
+    <t>4975218390</t>
   </si>
   <si>
     <t>Alteração de Conta Contábil CTe de Saída</t>
   </si>
   <si>
-    <t>21423</t>
+    <t>20/08/2023</t>
+  </si>
+  <si>
+    <t>5005070793</t>
   </si>
   <si>
     <t>Criar Nova KB com template responsivo</t>
   </si>
   <si>
-    <t>17/08/2023</t>
+    <t>21/08/2023</t>
   </si>
   <si>
     <t>Semana 3</t>
   </si>
   <si>
+    <t>5005079491</t>
+  </si>
+  <si>
     <t>Cadastro de documento</t>
   </si>
   <si>
+    <t>5005083774</t>
+  </si>
+  <si>
     <t>Cadastro de tipo de documentos</t>
   </si>
   <si>
+    <t>5005087463</t>
+  </si>
+  <si>
     <t>Cadastro de grupo de cargos</t>
   </si>
   <si>
+    <t>22/08/2023</t>
+  </si>
+  <si>
+    <t>5005090524</t>
+  </si>
+  <si>
     <t>Importar planilha de grupo de cargos</t>
   </si>
   <si>
+    <t>5005091990</t>
+  </si>
+  <si>
     <t>Pesquisa e visualização de documentos</t>
   </si>
   <si>
+    <t>5005094941</t>
+  </si>
+  <si>
     <t>Vincular com cadastro de cargos do Sistema Senior</t>
   </si>
   <si>
+    <t>5005096559</t>
+  </si>
+  <si>
     <t>Associar documento a grupo de cargo</t>
   </si>
   <si>
+    <t>5005098144</t>
+  </si>
+  <si>
     <t>Associar documento a tipo de documento</t>
   </si>
   <si>
+    <t>5005099507</t>
+  </si>
+  <si>
     <t>Possibilidade de trocar o documento e manter os cargos e tipo associados</t>
   </si>
   <si>
@@ -369,7 +426,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-17</t>
+    <t>Jul/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -1014,7 +1071,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1031,38 +1088,38 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
       </c>
@@ -1070,15 +1127,15 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1090,10 +1147,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1105,10 +1162,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1117,7 +1174,7 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -1125,22 +1182,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1152,10 +1209,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1164,45 +1221,45 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1211,62 +1268,62 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="O8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1278,10 +1335,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1293,10 +1350,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1305,15 +1362,15 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1325,10 +1382,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1340,10 +1397,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1352,15 +1409,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1372,10 +1429,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1387,10 +1444,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1399,15 +1456,15 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1419,10 +1476,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1434,10 +1491,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1446,15 +1503,15 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1466,10 +1523,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1481,10 +1538,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1493,15 +1550,15 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1513,10 +1570,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1528,7 +1585,7 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>24</v>
@@ -1540,33 +1597,33 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>21</v>
@@ -1575,10 +1632,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1587,46 +1644,46 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
       </c>
@@ -1634,15 +1691,15 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1654,10 +1711,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1669,10 +1726,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1681,15 +1738,15 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1701,10 +1758,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1716,10 +1773,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1728,15 +1785,15 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1748,10 +1805,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1763,10 +1820,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1775,15 +1832,15 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1795,10 +1852,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1810,10 +1867,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1822,15 +1879,15 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1842,10 +1899,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1857,7 +1914,7 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>24</v>
@@ -1869,15 +1926,15 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1889,10 +1946,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1904,7 +1961,7 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>24</v>
@@ -1916,15 +1973,15 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1936,10 +1993,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1951,10 +2008,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1963,15 +2020,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1983,10 +2040,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -1998,10 +2055,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2010,15 +2067,15 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2030,10 +2087,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2045,10 +2102,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2057,33 +2114,33 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>21</v>
@@ -2092,10 +2149,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2104,15 +2161,15 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2124,10 +2181,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2139,7 +2196,7 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>24</v>
@@ -2151,15 +2208,15 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2171,10 +2228,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2186,7 +2243,7 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>24</v>
@@ -2198,33 +2255,33 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>21</v>
@@ -2233,10 +2290,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2245,15 +2302,15 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2265,10 +2322,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2280,10 +2337,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2292,15 +2349,15 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2312,10 +2369,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2327,10 +2384,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2339,15 +2396,15 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2359,10 +2416,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2374,10 +2431,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2386,15 +2443,15 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2406,10 +2463,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2421,10 +2478,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2433,15 +2490,15 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2453,10 +2510,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2468,7 +2525,7 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>24</v>
@@ -2480,15 +2537,15 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2500,10 +2557,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2515,10 +2572,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2527,15 +2584,15 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2547,10 +2604,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2562,10 +2619,10 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2574,15 +2631,15 @@
         <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2594,10 +2651,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2609,10 +2666,10 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2621,15 +2678,15 @@
         <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2641,10 +2698,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2656,10 +2713,10 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2668,15 +2725,15 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2688,10 +2745,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2703,7 +2760,7 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>24</v>
@@ -2715,15 +2772,15 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2735,10 +2792,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2750,7 +2807,7 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>24</v>
@@ -2762,15 +2819,15 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2782,60 +2839,60 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="O41" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>21</v>
@@ -2844,10 +2901,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -2856,33 +2913,33 @@
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>21</v>
@@ -2891,10 +2948,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -2903,33 +2960,33 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>21</v>
@@ -2938,10 +2995,10 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -2950,10 +3007,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2969,23 +3026,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2993,16 +3050,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3013,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>11.51</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3021,7 +3078,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3034,7 +3091,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3042,7 +3099,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3073,12 +3130,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B2">
         <v>43</v>
@@ -3092,7 +3149,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3102,25 +3159,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3137,13 +3194,13 @@
         <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3155,21 +3212,21 @@
         <v>43</v>
       </c>
       <c r="P10" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H11">
         <v>4</v>
@@ -3181,21 +3238,21 @@
         <v>43</v>
       </c>
       <c r="M11" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="Q11">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -3207,73 +3264,61 @@
         <v>36</v>
       </c>
       <c r="J12" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="Q12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
-      <c r="P14" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q14">
-        <v>2</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3281,7 +3326,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3289,7 +3334,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3297,10 +3342,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3308,7 +3353,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3316,142 +3361,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>37</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>46</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
